--- a/public/sample/PSE_Portfolio_Sample.xlsx
+++ b/public/sample/PSE_Portfolio_Sample.xlsx
@@ -15,7 +15,8 @@
     <sheet name="Cash_Flows" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Benchmark_Constituents" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Stress_Scenarios" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Price_Override" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Price_History" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Price_Override" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -394,6 +395,64 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Trading date</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Stock code; use PSEI for the index</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Closing price, PHP</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Optional: dividend/split-adjusted close (used for VaR returns)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
     <comment ref="C1" authorId="0">
       <text>
         <r>
@@ -411,12 +470,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="226">
   <si>
     <t xml:space="preserve">PSE Portfolio Analytics — input workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload this workbook (exported from the PMS) to the app. Prices are fetched automatically from Yahoo Finance using the PSE ticker + '.PS' (e.g. BDO -&gt; BDO.PS); the benchmark index uses PSEI.PS.</t>
+    <t xml:space="preserve">Upload this workbook (exported from the PMS) to the app. Prices are fetched automatically from Yahoo Finance (EODHD for PSE stocks when the server has an API key; Yahoo Finance for the PSEi index), or read from the Price_History sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">ALL VALUES IN THIS SAMPLE ARE ILLUSTRATIVE (quantities, costs, fees, flows, benchmark weights and sector labels). Replace them with your PMS data and official PSE index weights before use.</t>
@@ -464,10 +523,16 @@
     <t xml:space="preserve">Optional. HISTORICAL rows replay actual returns between Start_Date and End_Date. SHOCK rows apply Shock_% to ALL, a sector name, or a single ticker.</t>
   </si>
   <si>
+    <t xml:space="preserve">Price_History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily closing prices from the PMS (Date, PSE_Ticker, Close, optional Adj_Close). Yahoo Finance no longer carries Philippine stocks, so supply this sheet unless the server has an EODHD API key. Use ticker PSEI for the index if you also want to supply it.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Price_Override</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional. Manual prices (suspended / illiquid / delisted names). Overrides Yahoo on that date.</t>
+    <t xml:space="preserve">Optional. Manual prices for single dates (suspended / illiquid names). Overrides every other source on that date.</t>
   </si>
   <si>
     <t xml:space="preserve">Colour code</t>
@@ -1059,6 +1124,24 @@
   </si>
   <si>
     <t xml:space="preserve">Historical windows are examples; stocks not listed at the time are proxied with the index move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adj_Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional, but needed for PSE stocks unless the server has an EODHD API key: Yahoo Finance no longer carries Philippine stocks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export daily closing prices from the PMS for every holding and benchmark member, about 3 years back from Valuation_Date (VaR lookback + backtest).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long format, one row per ticker per date. Tickers listed here are not fetched online. When prices come from this sheet, dividends must be entered as DIVIDEND rows in Transactions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete these note rows (or leave them: rows without a date and ticker are ignored).</t>
   </si>
   <si>
     <t xml:space="preserve">Reason</t>
@@ -1564,7 +1647,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1642,7 +1725,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>17</v>
       </c>
@@ -1656,6 +1739,14 @@
       </c>
       <c r="B13" s="7" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1683,238 +1774,238 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>46295</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>45930</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>46295</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>44928</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>500</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>0.94</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>10000</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>250</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>0.055</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1949,34 +2040,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1984,17 +2075,17 @@
         <v>45930</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" s="15" t="n">
         <v>60000</v>
@@ -2010,17 +2101,17 @@
         <v>45930</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>50000</v>
@@ -2036,17 +2127,17 @@
         <v>45930</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G4" s="15" t="n">
         <v>80000</v>
@@ -2062,17 +2153,17 @@
         <v>45930</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>20000</v>
@@ -2088,17 +2179,17 @@
         <v>45930</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>6000</v>
@@ -2114,17 +2205,17 @@
         <v>45930</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>98</v>
-      </c>
       <c r="F7" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>7000</v>
@@ -2140,17 +2231,17 @@
         <v>45930</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G8" s="15" t="n">
         <v>100000</v>
@@ -2166,17 +2257,17 @@
         <v>45930</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>250000</v>
@@ -2192,17 +2283,17 @@
         <v>45930</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>105</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>300000</v>
@@ -2218,17 +2309,17 @@
         <v>45930</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>120000</v>
@@ -2244,17 +2335,17 @@
         <v>45930</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>20000</v>
@@ -2270,17 +2361,17 @@
         <v>45930</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>40000</v>
@@ -2296,17 +2387,17 @@
         <v>45930</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>8000</v>
@@ -2322,17 +2413,17 @@
         <v>45930</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>2500</v>
@@ -2348,17 +2439,17 @@
         <v>45930</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>300000</v>
@@ -2374,17 +2465,17 @@
         <v>45930</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>60000</v>
@@ -2400,14 +2491,14 @@
         <v>45930</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="15" t="n">
@@ -2422,17 +2513,17 @@
         <v>46295</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>75000</v>
@@ -2446,17 +2537,17 @@
         <v>46295</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="G20" s="15" t="n">
         <v>50000</v>
@@ -2470,17 +2561,17 @@
         <v>46295</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>80000</v>
@@ -2494,17 +2585,17 @@
         <v>46295</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>23000</v>
@@ -2518,17 +2609,17 @@
         <v>46295</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>6000</v>
@@ -2542,17 +2633,17 @@
         <v>46295</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>98</v>
-      </c>
       <c r="F24" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G24" s="15" t="n">
         <v>7000</v>
@@ -2566,17 +2657,17 @@
         <v>46295</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>150000</v>
@@ -2590,17 +2681,17 @@
         <v>46295</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>105</v>
-      </c>
       <c r="F26" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>300000</v>
@@ -2614,17 +2705,17 @@
         <v>46295</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>120000</v>
@@ -2638,17 +2729,17 @@
         <v>46295</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G28" s="15" t="n">
         <v>20000</v>
@@ -2662,17 +2753,17 @@
         <v>46295</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>40000</v>
@@ -2686,17 +2777,17 @@
         <v>46295</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G30" s="15" t="n">
         <v>8000</v>
@@ -2710,17 +2801,17 @@
         <v>46295</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G31" s="15" t="n">
         <v>2500</v>
@@ -2734,17 +2825,17 @@
         <v>46295</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="G32" s="15" t="n">
         <v>150000</v>
@@ -2758,17 +2849,17 @@
         <v>46295</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>60000</v>
@@ -2782,17 +2873,17 @@
         <v>46295</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G34" s="15" t="n">
         <v>1500</v>
@@ -2806,17 +2897,17 @@
         <v>46295</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>40000</v>
@@ -2830,17 +2921,17 @@
         <v>46295</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G36" s="15" t="n">
         <v>100000</v>
@@ -2851,12 +2942,12 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2896,28 +2987,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2925,10 +3016,10 @@
         <v>45945</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
@@ -2937,7 +3028,7 @@
         <v>125000</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2945,10 +3036,10 @@
         <v>45975</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1500</v>
@@ -2959,7 +3050,7 @@
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2967,10 +3058,10 @@
         <v>46001</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>150000</v>
@@ -2981,7 +3072,7 @@
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2989,10 +3080,10 @@
         <v>46037</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
@@ -3001,7 +3092,7 @@
         <v>125000</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3009,10 +3100,10 @@
         <v>46042</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>15000</v>
@@ -3023,7 +3114,7 @@
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3031,10 +3122,10 @@
         <v>46070</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>100000</v>
@@ -3045,7 +3136,7 @@
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3053,10 +3144,10 @@
         <v>46090</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>40000</v>
@@ -3067,7 +3158,7 @@
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3075,10 +3166,10 @@
         <v>46127</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
@@ -3087,7 +3178,7 @@
         <v>125000</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3095,10 +3186,10 @@
         <v>46162</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>100000</v>
@@ -3109,7 +3200,7 @@
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,10 +3208,10 @@
         <v>46167</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>100000</v>
@@ -3131,7 +3222,7 @@
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3139,10 +3230,10 @@
         <v>46203</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
@@ -3151,7 +3242,7 @@
         <v>18500</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3159,10 +3250,10 @@
         <v>46218</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>
@@ -3171,7 +3262,7 @@
         <v>125000</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3179,10 +3270,10 @@
         <v>46246</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>3000</v>
@@ -3193,17 +3284,17 @@
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3239,16 +3330,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3259,10 +3350,10 @@
         <v>5000000</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3273,10 +3364,10 @@
         <v>2000000</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3314,30 +3405,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>14.36</v>
@@ -3346,13 +3437,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D3" s="18" t="n">
         <v>9.74</v>
@@ -3361,13 +3452,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>8.21</v>
@@ -3376,13 +3467,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>7.69</v>
@@ -3391,13 +3482,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>105</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>6.15</v>
@@ -3406,13 +3497,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>5.13</v>
@@ -3421,13 +3512,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>4.62</v>
@@ -3436,13 +3527,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>4.62</v>
@@ -3451,13 +3542,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>3.59</v>
@@ -3466,13 +3557,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>3.08</v>
@@ -3481,13 +3572,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>3.08</v>
@@ -3496,13 +3587,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>2.56</v>
@@ -3511,13 +3602,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>115</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>113</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>2.05</v>
@@ -3526,13 +3617,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>2.05</v>
@@ -3541,13 +3632,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>2.05</v>
@@ -3556,13 +3647,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>2.05</v>
@@ -3571,13 +3662,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>2.05</v>
@@ -3586,13 +3677,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>1.54</v>
@@ -3601,13 +3692,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D20" s="18" t="n">
         <v>1.54</v>
@@ -3616,13 +3707,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>1.54</v>
@@ -3631,13 +3722,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>1.54</v>
@@ -3646,13 +3737,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D23" s="18" t="n">
         <v>1.54</v>
@@ -3661,13 +3752,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>1.54</v>
@@ -3676,13 +3767,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" s="18" t="n">
         <v>1.54</v>
@@ -3691,13 +3782,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>1.03</v>
@@ -3706,13 +3797,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D27" s="18" t="n">
         <v>1.03</v>
@@ -3721,13 +3812,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D28" s="18" t="n">
         <v>1.03</v>
@@ -3736,13 +3827,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D29" s="18" t="n">
         <v>1.03</v>
@@ -3751,41 +3842,41 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D30" s="18" t="n">
         <v>1.03</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D31" s="18" t="n">
         <v>1.03</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D32" s="20" t="n">
         <f aca="false">SUM(D2:D31)</f>
@@ -3794,12 +3885,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3837,30 +3928,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="21"/>
@@ -3873,10 +3964,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="21"/>
@@ -3889,10 +3980,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>206</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="21"/>
@@ -3905,13 +3996,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>-20</v>
@@ -3921,13 +4012,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>210</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>-15</v>
@@ -3937,13 +4028,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" s="21" t="n">
         <v>-25</v>
@@ -3953,13 +4044,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" s="21" t="n">
         <v>-30</v>
@@ -3969,7 +4060,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3995,6 +4086,64 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4005,21 +4154,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
